--- a/事件列表.xlsx
+++ b/事件列表.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="23040" windowHeight="8580"/>
+    <workbookView windowWidth="22188" windowHeight="9180"/>
   </bookViews>
   <sheets>
     <sheet name="事件表" sheetId="1" r:id="rId1"/>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="40">
   <si>
     <t>事件ID</t>
   </si>
@@ -98,7 +98,7 @@
     <t>文件</t>
   </si>
   <si>
-    <t>incident-5c64c252-ce25-4584-bddf-eba401241a00</t>
+    <t>incident-5b352a72-af84-4d32-b70c-2ef2b6610af8</t>
   </si>
   <si>
     <t>主机存在Chopper 2014版PHP Webshell上传</t>
@@ -116,34 +116,37 @@
     <t>中危</t>
   </si>
   <si>
+    <t>处置完成</t>
+  </si>
+  <si>
+    <t>漏洞利用</t>
+  </si>
+  <si>
+    <t>WebShell管理工具</t>
+  </si>
+  <si>
+    <t>成功</t>
+  </si>
+  <si>
+    <t>中国华能集团有限公司福建分公司</t>
+  </si>
+  <si>
+    <t>129.37.235.168</t>
+  </si>
+  <si>
+    <t>1.1.1.1</t>
+  </si>
+  <si>
+    <t>STA (86A45542)</t>
+  </si>
+  <si>
+    <t>已推送</t>
+  </si>
+  <si>
+    <t>incident-5c64c252-ce26-4584-bddf-eba401241a00</t>
+  </si>
+  <si>
     <t>处置中</t>
-  </si>
-  <si>
-    <t>漏洞利用</t>
-  </si>
-  <si>
-    <t>WebShell管理工具</t>
-  </si>
-  <si>
-    <t>成功</t>
-  </si>
-  <si>
-    <t>中国华能集团有限公司福建分公司</t>
-  </si>
-  <si>
-    <t>129.37.235.168</t>
-  </si>
-  <si>
-    <t>1.1.1.1</t>
-  </si>
-  <si>
-    <t>STA (86A45542)</t>
-  </si>
-  <si>
-    <t>已推送</t>
-  </si>
-  <si>
-    <t>incident-5c64c252-ce26-4584-bddf-eba401241a00</t>
   </si>
   <si>
     <t>incident-5c64c252-ce27-4584-bddf-eba401241a00</t>
@@ -1359,7 +1362,7 @@
         <v>27</v>
       </c>
       <c r="G3" s="7" t="s">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="H3" s="3" t="s">
         <v>29</v>
@@ -1407,7 +1410,7 @@
     </row>
     <row r="4" customFormat="1" ht="24" customHeight="1" spans="1:21">
       <c r="A4" s="3" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B4" s="3" t="s">
         <v>23</v>
@@ -1425,7 +1428,7 @@
         <v>27</v>
       </c>
       <c r="G4" s="7" t="s">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="H4" s="3" t="s">
         <v>29</v>
@@ -1470,7 +1473,7 @@
     </row>
     <row r="5" customFormat="1" ht="24" customHeight="1" spans="1:22">
       <c r="A5" s="3" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B5" s="3" t="s">
         <v>23</v>
@@ -1488,7 +1491,7 @@
         <v>27</v>
       </c>
       <c r="G5" s="7" t="s">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="H5" s="3" t="s">
         <v>29</v>
@@ -1533,7 +1536,7 @@
     </row>
     <row r="6" customFormat="1" ht="24" customHeight="1" spans="1:20">
       <c r="A6" s="3" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B6" s="3" t="s">
         <v>23</v>
@@ -1549,7 +1552,7 @@
         <v>27</v>
       </c>
       <c r="G6" s="7" t="s">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="H6" s="3" t="s">
         <v>29</v>
